--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.03597122302158273</v>
+        <v>0.02142857142857143</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0.0352112676056338</v>
       </c>
       <c r="D2">
-        <v>0.9647887323943662</v>
+        <v>0.9716312056737588</v>
       </c>
       <c r="E2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
